--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127414920</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kälvjärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>848501</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7361730</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127414920</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127414920</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127414920</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127414920</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127414920</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127414920</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127414920</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127414920</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127414920</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,6 +890,218 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128340207</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80163</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kälvjärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>848508</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7361752</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128340208</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kälvjärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>848634</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7361773</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128340207</v>
       </c>
       <c r="B4" t="n">
-        <v>80163</v>
+        <v>80164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340208</v>
       </c>
       <c r="B5" t="n">
-        <v>91373</v>
+        <v>91378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128340207</v>
       </c>
       <c r="B4" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340208</v>
       </c>
       <c r="B5" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128340207</v>
       </c>
       <c r="B4" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340208</v>
       </c>
       <c r="B5" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128340207</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340208</v>
       </c>
       <c r="B5" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>128340208</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128340207</v>
       </c>
       <c r="B4" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340208</v>
       </c>
       <c r="B5" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128340207</v>
       </c>
       <c r="B4" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340208</v>
       </c>
       <c r="B5" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34385-2025 artfynd.xlsx
+++ b/artfynd/A 34385-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128340207</v>
       </c>
       <c r="B4" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340208</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
